--- a/artfynd/A 22307-2026 artfynd.xlsx
+++ b/artfynd/A 22307-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>902606</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512383.6394875059</v>
+        <v>512384</v>
       </c>
       <c r="R2" t="n">
-        <v>6952929.176910573</v>
+        <v>6952929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000500</v>
+        <v>1874605</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512418.4999739215</v>
+        <v>512433</v>
       </c>
       <c r="R3" t="n">
-        <v>6952703.046166873</v>
+        <v>6952748</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +857,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,37 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2000501</v>
+        <v>1874606</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -960,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512476.4098194052</v>
+        <v>512334</v>
       </c>
       <c r="R4" t="n">
-        <v>6952946.506996461</v>
+        <v>6952832</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,19 +958,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,37 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2000502</v>
+        <v>1874610</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512386.8823783355</v>
+        <v>512475</v>
       </c>
       <c r="R5" t="n">
-        <v>6952922.305082295</v>
+        <v>6952690</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1874605</v>
+        <v>1981469</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1192,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512433.0379233966</v>
+        <v>512446</v>
       </c>
       <c r="R6" t="n">
-        <v>6952748.079154225</v>
+        <v>6952752</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,19 +1160,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,37 +1193,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2073380</v>
+        <v>1981470</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1308,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512419.7249584997</v>
+        <v>512460</v>
       </c>
       <c r="R7" t="n">
-        <v>6952865.979197891</v>
+        <v>6953018</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,19 +1261,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,37 +1294,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2073379</v>
+        <v>2000500</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1424,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512420.2934787005</v>
+        <v>512418</v>
       </c>
       <c r="R8" t="n">
-        <v>6952714.985977197</v>
+        <v>6952703</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,19 +1362,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,15 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1981469</v>
+        <v>2000501</v>
       </c>
       <c r="B9" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1540,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512445.8912027818</v>
+        <v>512476</v>
       </c>
       <c r="R9" t="n">
-        <v>6952752.258247233</v>
+        <v>6952947</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,19 +1463,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,15 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1981470</v>
+        <v>2000502</v>
       </c>
       <c r="B10" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512459.5946937689</v>
+        <v>512387</v>
       </c>
       <c r="R10" t="n">
-        <v>6953018.035877498</v>
+        <v>6952922</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,19 +1564,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,6 +1594,320 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2073379</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kotjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512420</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6952715</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2073380</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kotjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>512420</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6952866</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15371166</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Märlingsbergets mångfaldspark, Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>512501</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6952931</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Typiska spår i 1 träd</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>grov tallöverståndare, mager barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22307-2026 artfynd.xlsx
+++ b/artfynd/A 22307-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/902606</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1874605</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1874606</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1874610</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1981469</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1981470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2000500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2000501</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2000502</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2073379</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2073380</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,8 +1968,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15371166</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>